--- a/coaching_forms/037_virtual_confidence_coaching_survey--coaching_forms.xlsx
+++ b/coaching_forms/037_virtual_confidence_coaching_survey--coaching_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>welcome_to_the_survey</t>
+          <t>Welcome to the Survey</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>how_would_you Describe_your_coaching_level</t>
+          <t>What is your current coaching level?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>what_areas_do_you_struggle_with</t>
+          <t>Which areas do you struggle with?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,35 +589,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>confidence_levels</t>
+          <t>confidence_areas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>what_areas_do_you_feel_confident_with</t>
+          <t>Where do you feel confident with?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>confidence_levels_1</t>
+          <t>self_efficacy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>self_confidence</t>
+          <t>Do you feel confident in taking action?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>confidence_levels_2</t>
+          <t>confidence_score_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>confidence_level</t>
+          <t>How would you rate your confidence score?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>confidence_levels_3</t>
+          <t>confidence_level</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>areas_confidence</t>
+          <t>What is your overall confidence level?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,35 +681,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>confidence_levels_4</t>
+          <t>self_confidence</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>self_confidence_level</t>
+          <t>How would you rate your self-confidence?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>self_efficacy</t>
+          <t>confidence_score_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>how_do_you Describe_your_self_efficacy</t>
+          <t>Confidence Score 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>self_efficacy_1</t>
+          <t>confidence_level_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>self</t>
+          <t>What is your confidence level?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>self_efficacy_2</t>
+          <t>self_confidence_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>Self Confidence 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>self_efficacy_3</t>
+          <t>confidence_area</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>self_efficacy</t>
+          <t>What is your confidence area?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>self_confidence_score</t>
+          <t>efficacy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>what_is_your_confidence_score</t>
+          <t>Do you feel confident in your abilities?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>self_confidence_score_1</t>
+          <t>self_efficacy_level</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>What is your level of self-efficacy?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,248 +842,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>self_confidence_score_2</t>
+          <t>confidence_self</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>confidence_score</t>
+          <t>How would you rate your confidence in yourself?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>self_confidence_score_3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>confidence_score</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>confidence_level</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>self_confidence_level</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>self_confidence_level</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>confidence_level_1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>confidence_level</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>self_confidence_levels</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>self_confidence_levels</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>self_confidence_level_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>confidence_level_1</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>self_confidence_levels_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>confidence_level_2</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>confidence_levels_3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>confidence_levels</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>confidence_levels_4</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>confidence_level_4</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>confidence_levels_5</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>confidence_levels_5</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,11 +868,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -1165,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1182,46 +952,46 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>confidence_levels_choices</t>
+          <t>confidence_areas_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>confidence_levels_choices</t>
+          <t>confidence_areas_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1020,46 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>efficacy_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>efficacy_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
